--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,9 +413,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I13"/>
+  <dimension ref="B1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
@@ -432,7 +433,6 @@
           <t>Москва</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -526,11 +526,6 @@
           <t>Сигарный клуб, 20к стандарт</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -570,7 +565,6 @@
           <t>С-Петербург</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Спикер</t>

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -660,7 +660,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Базовые стратегии РБ Про</t>
+          <t>Базовые стратегии АРБ Про</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Форум РБ Про "Базовые стратегии"</t>
+          <t>Форум АРБ Про "Базовые стратегии"</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Квартирник РБ Про</t>
+          <t>Квартирник АРБ Про</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Квартирник после форума РБ Про "Базовые стратегии". О главном без камер</t>
+          <t>Квартирник после форума АРБ Про "Базовые стратегии". О главном без камер</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">

--- a/data/events.xlsx
+++ b/data/events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="B1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -504,6 +504,11 @@
           <t>x</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>/breakfast/</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
